--- a/reports/Debug-snowbowl-20251216/For The Week Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20251216/For The Week Ending (Actual)_Revenue.xlsx
@@ -40,13 +40,13 @@
     <t xml:space="preserve">T101                     </t>
   </si>
   <si>
+    <t xml:space="preserve">T100                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T257                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">T103                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T100                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">T257                     </t>
   </si>
   <si>
     <t>Ski School</t>
@@ -524,7 +524,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="2">
-        <v>3762.3800</v>
+        <v>114125.7400</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="2">
-        <v>114125.7400</v>
+        <v>70.0000</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -552,7 +552,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="2">
-        <v>70.0000</v>
+        <v>3762.3800</v>
       </c>
     </row>
     <row r="7" spans="1:4">
